--- a/type_split_data_1981_2006_kopi.xlsx
+++ b/type_split_data_1981_2006_kopi.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/TEP4290-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5D5301-8348-724E-B225-ECAE5D8BB534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOL2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -531,23 +532,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
     <col min="2" max="27" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
@@ -627,7 +628,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
@@ -710,7 +711,7 @@
         <v>115794</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
@@ -793,7 +794,7 @@
         <v>1019387</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -876,7 +877,7 @@
         <v>346175</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
@@ -959,7 +960,7 @@
         <v>953320</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
@@ -1068,7 +1069,7 @@
         <v>2434676</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
@@ -1177,7 +1178,7 @@
         <v>4.7560332463128567E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
@@ -1286,7 +1287,7 @@
         <v>0.41869513643704542</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>35</v>
       </c>
@@ -1395,7 +1396,7 @@
         <v>0.14218524353959214</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>36</v>
       </c>
@@ -1504,7 +1505,7 @@
         <v>0.39155928756023389</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
@@ -1513,7 +1514,7 @@
         <v>6.2475503234593735E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
@@ -1522,7 +1523,7 @@
         <v>0.42311349413707461</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
@@ -1531,7 +1532,7 @@
         <v>0.11801937967162596</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1540,7 +1541,7 @@
         <v>0.39639162295670566</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="80" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A28" s="5" t="s">
         <v>32</v>
       </c>
